--- a/artfynd/A 32340-2025 artfynd.xlsx
+++ b/artfynd/A 32340-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94362117</v>
+        <v>94857923</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Gangelåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397690.3532408986</v>
+        <v>398051</v>
       </c>
       <c r="R2" t="n">
-        <v>6948811.882380342</v>
+        <v>6948543</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94361317</v>
+        <v>94362117</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397750.9320768502</v>
+        <v>397690</v>
       </c>
       <c r="R3" t="n">
-        <v>6948923.624036693</v>
+        <v>6948812</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +841,9 @@
           <t>2021-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94812020</v>
+        <v>94813951</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,41 +881,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398096.2984548429</v>
+        <v>398034</v>
       </c>
       <c r="R4" t="n">
-        <v>6948964.930514643</v>
+        <v>6948627</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,19 +939,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,49 +956,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94811997</v>
+        <v>94812239</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1004,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398108.3766975648</v>
+        <v>398071</v>
       </c>
       <c r="R5" t="n">
-        <v>6948968.237749142</v>
+        <v>6948870</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,19 +1037,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,54 +1066,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94811759</v>
+        <v>94857921</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Gangelåsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398111.422920256</v>
+        <v>398027</v>
       </c>
       <c r="R6" t="n">
-        <v>6949037.138617595</v>
+        <v>6948598</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,19 +1134,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,66 +1151,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94811867</v>
+        <v>94857914</v>
       </c>
       <c r="B7" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Gangelåsen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398105.5066697927</v>
+        <v>398056</v>
       </c>
       <c r="R7" t="n">
-        <v>6949114.133634569</v>
+        <v>6948541</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,54 +1231,40 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94811862</v>
+        <v>94811687</v>
       </c>
       <c r="B8" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398105.5066697927</v>
+        <v>398086</v>
       </c>
       <c r="R8" t="n">
-        <v>6949114.133634569</v>
+        <v>6949132</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,19 +1330,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94812040</v>
+        <v>94811759</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398104.7793718915</v>
+        <v>398111</v>
       </c>
       <c r="R9" t="n">
-        <v>6948941.210341037</v>
+        <v>6949037</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,19 +1428,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94811999</v>
+        <v>94811862</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,21 +1468,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1493,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398108.3766975648</v>
+        <v>398106</v>
       </c>
       <c r="R10" t="n">
-        <v>6948968.237749142</v>
+        <v>6949115</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,19 +1526,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,27 +1543,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94811757</v>
+        <v>94813005</v>
       </c>
       <c r="B11" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1566,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398111.422920256</v>
+        <v>398106</v>
       </c>
       <c r="R11" t="n">
-        <v>6949037.138617595</v>
+        <v>6948716</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1764,7 +1616,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tännäs</t>
+          <t>Hede</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1772,19 +1624,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,15 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94813952</v>
+        <v>94812040</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1852,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398034.7514793283</v>
+        <v>398104</v>
       </c>
       <c r="R12" t="n">
-        <v>6948627.353438853</v>
+        <v>6948941</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,19 +1722,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,37 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94812239</v>
+        <v>94361317</v>
       </c>
       <c r="B13" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398070.7861902009</v>
+        <v>397751</v>
       </c>
       <c r="R13" t="n">
-        <v>6948869.582214885</v>
+        <v>6948924</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,22 +1817,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,15 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94811761</v>
+        <v>94812430</v>
       </c>
       <c r="B14" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398111.422920256</v>
+        <v>398121</v>
       </c>
       <c r="R14" t="n">
-        <v>6949037.138617595</v>
+        <v>6948858</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2111,19 +1918,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,15 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94812337</v>
+        <v>94813806</v>
       </c>
       <c r="B15" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,21 +1958,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +1983,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398070.7861902009</v>
+        <v>398086</v>
       </c>
       <c r="R15" t="n">
-        <v>6948869.582214885</v>
+        <v>6948673</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2224,19 +2016,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,54 +2045,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94813951</v>
+        <v>94857916</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Gangelåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398034.7514793283</v>
+        <v>398040</v>
       </c>
       <c r="R16" t="n">
-        <v>6948627.353438853</v>
+        <v>6948655</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,19 +2113,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,27 +2130,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94857923</v>
+        <v>94811757</v>
       </c>
       <c r="B17" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,37 +2153,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gangelåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398050.5659068179</v>
+        <v>398111</v>
       </c>
       <c r="R17" t="n">
-        <v>6948542.681076197</v>
+        <v>6949037</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2449,19 +2211,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,65 +2228,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94857921</v>
+        <v>94812337</v>
       </c>
       <c r="B18" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gangelåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398026.9402293859</v>
+        <v>398071</v>
       </c>
       <c r="R18" t="n">
-        <v>6948598.153203294</v>
+        <v>6948870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,19 +2309,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,65 +2326,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94857916</v>
+        <v>94812020</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gangelåsen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398040.190542318</v>
+        <v>398096</v>
       </c>
       <c r="R19" t="n">
-        <v>6948654.326555897</v>
+        <v>6948965</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,19 +2413,9 @@
           <t>2021-07-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,15 +2430,707 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Bjarne Tutturen, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>94813830</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>398099</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6948714</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94811761</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>398111</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6949037</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94811867</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>398106</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6949115</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>94811999</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>398108</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6948968</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94813002</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>398106</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6948716</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>94813799</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>398086</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6948673</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94361732</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>397743</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6948892</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32340-2025 artfynd.xlsx
+++ b/artfynd/A 32340-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94362117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94361317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94361732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94857923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813951</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94857921</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94857914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1454,6 +1494,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1552,6 +1597,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1649,6 +1699,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94857916</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813830</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813002</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94813799</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94812239</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811862</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2439,6 +2529,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94812040</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94812430</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811757</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2733,6 +2838,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94812337</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2837,6 +2947,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94812020</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811761</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3033,6 +3153,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811867</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,8 +3256,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94811999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>